--- a/HPT Resource Index.xlsx
+++ b/HPT Resource Index.xlsx
@@ -610,7 +610,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL372"/>
+  <dimension ref="A1:AL374"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="12.33203125" customWidth="1" min="1" max="1"/>
@@ -72047,8 +72047,337 @@
         </is>
       </c>
     </row>
-    <row r="373" ht="13" customHeight="1"/>
-    <row r="374" ht="13" customHeight="1"/>
+    <row r="373" ht="13" customHeight="1">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Tewogbola2025-ins</t>
+        </is>
+      </c>
+      <c r="B373" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>medRxiv (preprint)</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>10.1101/2025.08.27.25334236</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>https://www.medrxiv.org/content/10.1101/2025.08.27.25334236v1</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>Preprint</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>Health insurance</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>Health &amp; Prevention</t>
+        </is>
+      </c>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>Between-subjects</t>
+        </is>
+      </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M373" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N373" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="O373" t="inlineStr">
+        <is>
+          <t>Africa</t>
+        </is>
+      </c>
+      <c r="P373" t="n">
+        <v>106</v>
+      </c>
+      <c r="Q373" t="inlineStr">
+        <is>
+          <t>General community sample (Nigerian adults)</t>
+        </is>
+      </c>
+      <c r="R373" t="n">
+        <v>29.48</v>
+      </c>
+      <c r="S373" t="n">
+        <v>15</v>
+      </c>
+      <c r="T373" t="n">
+        <v>5</v>
+      </c>
+      <c r="U373" t="n">
+        <v>560000</v>
+      </c>
+      <c r="V373" t="inlineStr">
+        <is>
+          <t>NGN</t>
+        </is>
+      </c>
+      <c r="W373" t="inlineStr">
+        <is>
+          <t>Koffarnus et al. exponentiated model</t>
+        </is>
+      </c>
+      <c r="X373" t="inlineStr">
+        <is>
+          <t>Empirical</t>
+        </is>
+      </c>
+      <c r="Y373" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z373" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA373" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="AB373" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC373" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD373" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE373" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF373" t="inlineStr">
+        <is>
+          <t>AUC (used as individual-level demand proxy; Q0/alpha could not be fit per-individual on dichotomous Yes/No responses)</t>
+        </is>
+      </c>
+      <c r="AG373" t="n">
+        <v>6.3e-05</v>
+      </c>
+      <c r="AH373" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="AJ373" t="n">
+        <v>18478.78</v>
+      </c>
+      <c r="AK373" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AL373" t="inlineStr">
+        <is>
+          <t>Preprint, self-authored by the PI (PROMISE Labs Africa). Aggregate exponential/exponentiated demand model fit to pooled Yes/No purchase responses across all 106 participants (Figure 1); individual-level Q0/alpha could not be estimated from dichotomous responses, so a normalized AUC was used as an individual-level proxy instead. Values here are the full-sample aggregate model, not the open/closed-economy subgroup splits reported separately in the paper.</t>
+        </is>
+      </c>
+    </row>
+    <row r="374" ht="13" customHeight="1">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Tewogbola2025-mil</t>
+        </is>
+      </c>
+      <c r="B374" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>SSRN (preprint)</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>10.2139/ssrn.7167500</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>https://papers.ssrn.com/sol3/papers.cfm?abstract_id=7167500</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>Preprint</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>Support for U.S. military intervention</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>Cross-sectional</t>
+        </is>
+      </c>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M374" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N374" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="O374" t="inlineStr">
+        <is>
+          <t>Africa</t>
+        </is>
+      </c>
+      <c r="P374" t="n">
+        <v>106</v>
+      </c>
+      <c r="Q374" t="inlineStr">
+        <is>
+          <t>General community sample (Nigerian adults)</t>
+        </is>
+      </c>
+      <c r="R374" t="n">
+        <v>30.03</v>
+      </c>
+      <c r="S374" t="n">
+        <v>10</v>
+      </c>
+      <c r="T374" t="n">
+        <v>0</v>
+      </c>
+      <c r="U374" t="n">
+        <v>100</v>
+      </c>
+      <c r="V374" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W374" t="inlineStr">
+        <is>
+          <t>Koffarnus et al. exponentiated model</t>
+        </is>
+      </c>
+      <c r="X374" t="inlineStr">
+        <is>
+          <t>Empirical</t>
+        </is>
+      </c>
+      <c r="Y374" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z374" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA374" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="AB374" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC374" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD374" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE374" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF374" t="inlineStr">
+        <is>
+          <t>P50 = 16.87% (likelihood of success at which the fitted model predicts 50% support)</t>
+        </is>
+      </c>
+      <c r="AG374" t="n">
+        <v>0.000155</v>
+      </c>
+      <c r="AH374" t="n">
+        <v>61.85</v>
+      </c>
+      <c r="AK374" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AL374" t="inlineStr">
+        <is>
+          <t>Preprint, self-authored by the PI (PROMISE Labs Africa). Not a purchase/consumption commodity -- an HPT-style demand curve applied to policy support, with likelihood of successful violence suppression (100%-0%) substituted for monetary price (modeled as odds against success). lowest_price/highest_price above represent that 0-100% likelihood scale, not currency. Included per the site's stated scope allowance for non-monetary price substitutes, but it is the furthest stretch of "commodity" in the index so far -- flagged for reconsideration if that scope guidance changes. Values are the full-sample aggregate model (N=106), not the demographic subgroup splits reported separately in the paper.</t>
+        </is>
+      </c>
+    </row>
     <row r="375" ht="13" customHeight="1"/>
     <row r="376" ht="13" customHeight="1"/>
     <row r="377" ht="13" customHeight="1"/>

--- a/HPT Resource Index.xlsx
+++ b/HPT Resource Index.xlsx
@@ -72122,7 +72122,7 @@
         </is>
       </c>
       <c r="P373" t="n">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="Q373" t="inlineStr">
         <is>
@@ -72210,7 +72210,7 @@
       </c>
       <c r="AL373" t="inlineStr">
         <is>
-          <t>Preprint, self-authored by the PI (PROMISE Labs Africa). Aggregate exponential/exponentiated demand model fit to pooled Yes/No purchase responses across all 106 participants (Figure 1); individual-level Q0/alpha could not be estimated from dichotomous responses, so a normalized AUC was used as an individual-level proxy instead. Values here are the full-sample aggregate model, not the open/closed-economy subgroup splits reported separately in the paper.</t>
+          <t>Preprint, self-authored by the PI (PROMISE Labs Africa); still under peer review, sample size may be revised once a final accepted version exists. N=78 used here (not the N=106 total recruited) -- Table 1 reports 106 for most characteristics, but Economy Type Assigned To (the experimental condition the demand analysis is split on) and Household Income both sum to only 78 with no accounting for the other 28, so 78 is treated as the analyzed sample. Aggregate exponential/exponentiated demand model fit to pooled Yes/No purchase responses (Figure 1); individual-level Q0/alpha could not be estimated from dichotomous responses, so a normalized AUC was used as an individual-level proxy instead. Values here are the full-sample aggregate model, not the open/closed-economy subgroup splits reported separately in the paper.</t>
         </is>
       </c>
     </row>

--- a/HPT Resource Index.xlsx
+++ b/HPT Resource Index.xlsx
@@ -610,7 +610,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL374"/>
+  <dimension ref="A1:AL377"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="12.33203125" customWidth="1" min="1" max="1"/>
@@ -72378,9 +72378,498 @@
         </is>
       </c>
     </row>
-    <row r="375" ht="13" customHeight="1"/>
-    <row r="376" ht="13" customHeight="1"/>
-    <row r="377" ht="13" customHeight="1"/>
+    <row r="375" ht="13" customHeight="1">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>Goto2026-ct</t>
+        </is>
+      </c>
+      <c r="B375" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>bioRxiv (preprint)</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>10.64898/2026.07.26.740843</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.64898/2026.07.26.740843</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>Preprint</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>Snack food</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>Food &amp; Nutrition</t>
+        </is>
+      </c>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>Cross-sectional</t>
+        </is>
+      </c>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M375" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N375" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="O375" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="P375" t="n">
+        <v>52</v>
+      </c>
+      <c r="Q375" t="inlineStr">
+        <is>
+          <t>General community sample (no criminal record)</t>
+        </is>
+      </c>
+      <c r="S375" t="n">
+        <v>9</v>
+      </c>
+      <c r="T375" t="n">
+        <v>0</v>
+      </c>
+      <c r="U375" t="n">
+        <v>5000</v>
+      </c>
+      <c r="V375" t="inlineStr">
+        <is>
+          <t>JPY</t>
+        </is>
+      </c>
+      <c r="W375" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="X375" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Y375" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z375" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA375" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="AB375" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC375" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD375" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE375" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF375" t="inlineStr">
+        <is>
+          <t>Omax (maximum expenditure)</t>
+        </is>
+      </c>
+      <c r="AG375" t="n">
+        <v>0.446</v>
+      </c>
+      <c r="AH375" t="n">
+        <v>20.66</v>
+      </c>
+      <c r="AI375" t="n">
+        <v>1740</v>
+      </c>
+      <c r="AJ375" t="n">
+        <v>348.9</v>
+      </c>
+      <c r="AL375" t="inlineStr">
+        <is>
+          <t>Not self-authored -- independent Japan-based group (Kyoto University et al.), bioRxiv preprint, not yet peer-reviewed. Three-group study (theft recidivists with/without kleptomania vs. healthy controls); coded as 3 rows since averaging clinical and control groups would misrepresent the finding (the study's point is the group difference), same pattern used for multi-commodity papers split by commodity. Commodity is a self-nominated favorite snack/sweet (not a fixed item), coded as "Snack food". Demand model equation not stated in the main text (paper reports indices Q0, alpha, Omax, Pmax, breakpoint without citing a specific curve-fitting equation); R2 not reported anywhere. Mean age not broken out by group in the main text (only a combined TR-vs-CT test was reported: not significantly different). Also administered a balloon analogue risk task (BART) with fNIRS measurement of prefrontal cortex activity -- out of HPT scope, not coded here. First Japan/JPY/Asia entries in the index. This row: control (CT) group.</t>
+        </is>
+      </c>
+    </row>
+    <row r="376" ht="13" customHeight="1">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Goto2026-trnk</t>
+        </is>
+      </c>
+      <c r="B376" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>bioRxiv (preprint)</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>10.64898/2026.07.26.740843</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.64898/2026.07.26.740843</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>Preprint</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>Snack food</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>Food &amp; Nutrition</t>
+        </is>
+      </c>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>Cross-sectional</t>
+        </is>
+      </c>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M376" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N376" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="O376" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="P376" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q376" t="inlineStr">
+        <is>
+          <t>Theft recidivists without kleptomania</t>
+        </is>
+      </c>
+      <c r="S376" t="n">
+        <v>9</v>
+      </c>
+      <c r="T376" t="n">
+        <v>0</v>
+      </c>
+      <c r="U376" t="n">
+        <v>5000</v>
+      </c>
+      <c r="V376" t="inlineStr">
+        <is>
+          <t>JPY</t>
+        </is>
+      </c>
+      <c r="W376" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="X376" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Y376" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z376" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA376" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="AB376" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC376" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD376" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE376" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF376" t="inlineStr">
+        <is>
+          <t>Omax (maximum expenditure)</t>
+        </is>
+      </c>
+      <c r="AG376" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="AH376" t="n">
+        <v>76.34999999999999</v>
+      </c>
+      <c r="AI376" t="n">
+        <v>1694</v>
+      </c>
+      <c r="AJ376" t="n">
+        <v>293.8</v>
+      </c>
+      <c r="AL376" t="inlineStr">
+        <is>
+          <t>Not self-authored -- independent Japan-based group (Kyoto University et al.), bioRxiv preprint, not yet peer-reviewed. Three-group study (theft recidivists with/without kleptomania vs. healthy controls); coded as 3 rows since averaging clinical and control groups would misrepresent the finding (the study's point is the group difference), same pattern used for multi-commodity papers split by commodity. Commodity is a self-nominated favorite snack/sweet (not a fixed item), coded as "Snack food". Demand model equation not stated in the main text (paper reports indices Q0, alpha, Omax, Pmax, breakpoint without citing a specific curve-fitting equation); R2 not reported anywhere. Mean age not broken out by group in the main text (only a combined TR-vs-CT test was reported: not significantly different). Also administered a balloon analogue risk task (BART) with fNIRS measurement of prefrontal cortex activity -- out of HPT scope, not coded here. First Japan/JPY/Asia entries in the index. This row: theft recidivists without kleptomania (TR-NK).</t>
+        </is>
+      </c>
+    </row>
+    <row r="377" ht="13" customHeight="1">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Goto2026-trka</t>
+        </is>
+      </c>
+      <c r="B377" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>bioRxiv (preprint)</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>10.64898/2026.07.26.740843</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.64898/2026.07.26.740843</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>Preprint</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>Snack food</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>Food &amp; Nutrition</t>
+        </is>
+      </c>
+      <c r="J377" t="inlineStr">
+        <is>
+          <t>Cross-sectional</t>
+        </is>
+      </c>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M377" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N377" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="O377" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="P377" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q377" t="inlineStr">
+        <is>
+          <t>Theft recidivists with kleptomania</t>
+        </is>
+      </c>
+      <c r="S377" t="n">
+        <v>9</v>
+      </c>
+      <c r="T377" t="n">
+        <v>0</v>
+      </c>
+      <c r="U377" t="n">
+        <v>5000</v>
+      </c>
+      <c r="V377" t="inlineStr">
+        <is>
+          <t>JPY</t>
+        </is>
+      </c>
+      <c r="W377" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="X377" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Y377" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z377" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA377" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="AB377" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC377" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD377" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE377" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF377" t="inlineStr">
+        <is>
+          <t>Omax (maximum expenditure)</t>
+        </is>
+      </c>
+      <c r="AG377" t="n">
+        <v>0.601</v>
+      </c>
+      <c r="AH377" t="n">
+        <v>112.3</v>
+      </c>
+      <c r="AI377" t="n">
+        <v>1838</v>
+      </c>
+      <c r="AJ377" t="n">
+        <v>124.9</v>
+      </c>
+      <c r="AL377" t="inlineStr">
+        <is>
+          <t>Not self-authored -- independent Japan-based group (Kyoto University et al.), bioRxiv preprint, not yet peer-reviewed. Three-group study (theft recidivists with/without kleptomania vs. healthy controls); coded as 3 rows since averaging clinical and control groups would misrepresent the finding (the study's point is the group difference), same pattern used for multi-commodity papers split by commodity. Commodity is a self-nominated favorite snack/sweet (not a fixed item), coded as "Snack food". Demand model equation not stated in the main text (paper reports indices Q0, alpha, Omax, Pmax, breakpoint without citing a specific curve-fitting equation); R2 not reported anywhere. Mean age not broken out by group in the main text (only a combined TR-vs-CT test was reported: not significantly different). Also administered a balloon analogue risk task (BART) with fNIRS measurement of prefrontal cortex activity -- out of HPT scope, not coded here. First Japan/JPY/Asia entries in the index. This row: theft recidivists with kleptomania (TR-KA).</t>
+        </is>
+      </c>
+    </row>
     <row r="378" ht="13" customHeight="1"/>
     <row r="379" ht="13" customHeight="1"/>
     <row r="380" ht="13" customHeight="1"/>

--- a/HPT Resource Index.xlsx
+++ b/HPT Resource Index.xlsx
@@ -610,7 +610,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL377"/>
+  <dimension ref="A1:AL375"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="12.33203125" customWidth="1" min="1" max="1"/>
@@ -72381,7 +72381,7 @@
     <row r="375" ht="13" customHeight="1">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Goto2026-ct</t>
+          <t>Goto2026</t>
         </is>
       </c>
       <c r="B375" t="n">
@@ -72453,11 +72453,11 @@
         </is>
       </c>
       <c r="P375" t="n">
-        <v>52</v>
+        <v>108</v>
       </c>
       <c r="Q375" t="inlineStr">
         <is>
-          <t>General community sample (no criminal record)</t>
+          <t>Combined: control subjects with no criminal record, theft recidivists without kleptomania, and theft recidivists with kleptomania</t>
         </is>
       </c>
       <c r="S375" t="n">
@@ -72525,351 +72525,25 @@
         </is>
       </c>
       <c r="AG375" t="n">
-        <v>0.446</v>
+        <v>0.487</v>
       </c>
       <c r="AH375" t="n">
-        <v>20.66</v>
+        <v>69.77</v>
       </c>
       <c r="AI375" t="n">
-        <v>1740</v>
+        <v>1757.33</v>
       </c>
       <c r="AJ375" t="n">
-        <v>348.9</v>
+        <v>255.87</v>
       </c>
       <c r="AL375" t="inlineStr">
         <is>
-          <t>Not self-authored -- independent Japan-based group (Kyoto University et al.), bioRxiv preprint, not yet peer-reviewed. Three-group study (theft recidivists with/without kleptomania vs. healthy controls); coded as 3 rows since averaging clinical and control groups would misrepresent the finding (the study's point is the group difference), same pattern used for multi-commodity papers split by commodity. Commodity is a self-nominated favorite snack/sweet (not a fixed item), coded as "Snack food". Demand model equation not stated in the main text (paper reports indices Q0, alpha, Omax, Pmax, breakpoint without citing a specific curve-fitting equation); R2 not reported anywhere. Mean age not broken out by group in the main text (only a combined TR-vs-CT test was reported: not significantly different). Also administered a balloon analogue risk task (BART) with fNIRS measurement of prefrontal cortex activity -- out of HPT scope, not coded here. First Japan/JPY/Asia entries in the index. This row: control (CT) group.</t>
+          <t>Not self-authored -- independent Japan-based group (Kyoto University et al.), bioRxiv preprint, not yet peer-reviewed. Original paper reports 3 separate populations (control N=52, theft recidivists without kleptomania N=40, theft recidivists with kleptomania N=16) with distinct Q0/alpha/Omax/Pmax/breakpoint per group -- collapsed here into one row: N summed (108), indices averaged (simple mean across the 3 groups, not N-weighted). This obscures the paper's actual finding, which is the group difference (kleptomania group showed markedly higher Q0, alpha, and breakpoint than the other two) -- see the paper directly for the real per-group values. Commodity is a self-nominated favorite snack/sweet (not a fixed item), coded as "Snack food". Demand model equation not stated in the main text; R2 not reported. Mean age not broken out by group. Also administered a balloon analogue risk task (BART) with fNIRS measurement of prefrontal cortex activity -- out of HPT scope, not coded here. First Japan/JPY/Asia entries in the index.</t>
         </is>
       </c>
     </row>
-    <row r="376" ht="13" customHeight="1">
-      <c r="A376" t="inlineStr">
-        <is>
-          <t>Goto2026-trnk</t>
-        </is>
-      </c>
-      <c r="B376" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C376" t="inlineStr">
-        <is>
-          <t>bioRxiv (preprint)</t>
-        </is>
-      </c>
-      <c r="D376" t="inlineStr">
-        <is>
-          <t>10.64898/2026.07.26.740843</t>
-        </is>
-      </c>
-      <c r="E376" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.64898/2026.07.26.740843</t>
-        </is>
-      </c>
-      <c r="F376" t="inlineStr">
-        <is>
-          <t>Preprint</t>
-        </is>
-      </c>
-      <c r="G376" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H376" t="inlineStr">
-        <is>
-          <t>Snack food</t>
-        </is>
-      </c>
-      <c r="I376" t="inlineStr">
-        <is>
-          <t>Food &amp; Nutrition</t>
-        </is>
-      </c>
-      <c r="J376" t="inlineStr">
-        <is>
-          <t>Cross-sectional</t>
-        </is>
-      </c>
-      <c r="K376" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
-      <c r="L376" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M376" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N376" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="O376" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="P376" t="n">
-        <v>40</v>
-      </c>
-      <c r="Q376" t="inlineStr">
-        <is>
-          <t>Theft recidivists without kleptomania</t>
-        </is>
-      </c>
-      <c r="S376" t="n">
-        <v>9</v>
-      </c>
-      <c r="T376" t="n">
-        <v>0</v>
-      </c>
-      <c r="U376" t="n">
-        <v>5000</v>
-      </c>
-      <c r="V376" t="inlineStr">
-        <is>
-          <t>JPY</t>
-        </is>
-      </c>
-      <c r="W376" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="X376" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="Y376" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z376" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA376" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="AB376" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC376" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD376" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AE376" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF376" t="inlineStr">
-        <is>
-          <t>Omax (maximum expenditure)</t>
-        </is>
-      </c>
-      <c r="AG376" t="n">
-        <v>0.414</v>
-      </c>
-      <c r="AH376" t="n">
-        <v>76.34999999999999</v>
-      </c>
-      <c r="AI376" t="n">
-        <v>1694</v>
-      </c>
-      <c r="AJ376" t="n">
-        <v>293.8</v>
-      </c>
-      <c r="AL376" t="inlineStr">
-        <is>
-          <t>Not self-authored -- independent Japan-based group (Kyoto University et al.), bioRxiv preprint, not yet peer-reviewed. Three-group study (theft recidivists with/without kleptomania vs. healthy controls); coded as 3 rows since averaging clinical and control groups would misrepresent the finding (the study's point is the group difference), same pattern used for multi-commodity papers split by commodity. Commodity is a self-nominated favorite snack/sweet (not a fixed item), coded as "Snack food". Demand model equation not stated in the main text (paper reports indices Q0, alpha, Omax, Pmax, breakpoint without citing a specific curve-fitting equation); R2 not reported anywhere. Mean age not broken out by group in the main text (only a combined TR-vs-CT test was reported: not significantly different). Also administered a balloon analogue risk task (BART) with fNIRS measurement of prefrontal cortex activity -- out of HPT scope, not coded here. First Japan/JPY/Asia entries in the index. This row: theft recidivists without kleptomania (TR-NK).</t>
-        </is>
-      </c>
-    </row>
-    <row r="377" ht="13" customHeight="1">
-      <c r="A377" t="inlineStr">
-        <is>
-          <t>Goto2026-trka</t>
-        </is>
-      </c>
-      <c r="B377" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C377" t="inlineStr">
-        <is>
-          <t>bioRxiv (preprint)</t>
-        </is>
-      </c>
-      <c r="D377" t="inlineStr">
-        <is>
-          <t>10.64898/2026.07.26.740843</t>
-        </is>
-      </c>
-      <c r="E377" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.64898/2026.07.26.740843</t>
-        </is>
-      </c>
-      <c r="F377" t="inlineStr">
-        <is>
-          <t>Preprint</t>
-        </is>
-      </c>
-      <c r="G377" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H377" t="inlineStr">
-        <is>
-          <t>Snack food</t>
-        </is>
-      </c>
-      <c r="I377" t="inlineStr">
-        <is>
-          <t>Food &amp; Nutrition</t>
-        </is>
-      </c>
-      <c r="J377" t="inlineStr">
-        <is>
-          <t>Cross-sectional</t>
-        </is>
-      </c>
-      <c r="K377" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
-      <c r="L377" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M377" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N377" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="O377" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="P377" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q377" t="inlineStr">
-        <is>
-          <t>Theft recidivists with kleptomania</t>
-        </is>
-      </c>
-      <c r="S377" t="n">
-        <v>9</v>
-      </c>
-      <c r="T377" t="n">
-        <v>0</v>
-      </c>
-      <c r="U377" t="n">
-        <v>5000</v>
-      </c>
-      <c r="V377" t="inlineStr">
-        <is>
-          <t>JPY</t>
-        </is>
-      </c>
-      <c r="W377" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="X377" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="Y377" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z377" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA377" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="AB377" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC377" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD377" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AE377" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF377" t="inlineStr">
-        <is>
-          <t>Omax (maximum expenditure)</t>
-        </is>
-      </c>
-      <c r="AG377" t="n">
-        <v>0.601</v>
-      </c>
-      <c r="AH377" t="n">
-        <v>112.3</v>
-      </c>
-      <c r="AI377" t="n">
-        <v>1838</v>
-      </c>
-      <c r="AJ377" t="n">
-        <v>124.9</v>
-      </c>
-      <c r="AL377" t="inlineStr">
-        <is>
-          <t>Not self-authored -- independent Japan-based group (Kyoto University et al.), bioRxiv preprint, not yet peer-reviewed. Three-group study (theft recidivists with/without kleptomania vs. healthy controls); coded as 3 rows since averaging clinical and control groups would misrepresent the finding (the study's point is the group difference), same pattern used for multi-commodity papers split by commodity. Commodity is a self-nominated favorite snack/sweet (not a fixed item), coded as "Snack food". Demand model equation not stated in the main text (paper reports indices Q0, alpha, Omax, Pmax, breakpoint without citing a specific curve-fitting equation); R2 not reported anywhere. Mean age not broken out by group in the main text (only a combined TR-vs-CT test was reported: not significantly different). Also administered a balloon analogue risk task (BART) with fNIRS measurement of prefrontal cortex activity -- out of HPT scope, not coded here. First Japan/JPY/Asia entries in the index. This row: theft recidivists with kleptomania (TR-KA).</t>
-        </is>
-      </c>
-    </row>
+    <row r="376" ht="13" customHeight="1"/>
+    <row r="377" ht="13" customHeight="1"/>
     <row r="378" ht="13" customHeight="1"/>
     <row r="379" ht="13" customHeight="1"/>
     <row r="380" ht="13" customHeight="1"/>

--- a/HPT Resource Index.xlsx
+++ b/HPT Resource Index.xlsx
@@ -610,7 +610,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL375"/>
+  <dimension ref="A1:AL376"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="12.33203125" customWidth="1" min="1" max="1"/>
@@ -72542,7 +72542,177 @@
         </is>
       </c>
     </row>
-    <row r="376" ht="13" customHeight="1"/>
+    <row r="376" ht="13" customHeight="1">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Yang2024</t>
+        </is>
+      </c>
+      <c r="B376" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>Journal of Peking University (Health Sciences)</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>10.19723/j.issn.1671-167X.2024.03.015</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.19723/j.issn.1671-167X.2024.03.015</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>Peer-Reviewed</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>Cigarettes</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>Tobacco &amp; Nicotine</t>
+        </is>
+      </c>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>Secondary analysis</t>
+        </is>
+      </c>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M376" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N376" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="O376" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="P376" t="n">
+        <v>447</v>
+      </c>
+      <c r="Q376" t="inlineStr">
+        <is>
+          <t>Adult male smokers (coal mining/manufacturing/energy industries; Jiangsu, Inner Mongolia, Hebei)</t>
+        </is>
+      </c>
+      <c r="R376" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="S376" t="n">
+        <v>13</v>
+      </c>
+      <c r="T376" t="n">
+        <v>0</v>
+      </c>
+      <c r="U376" t="n">
+        <v>600</v>
+      </c>
+      <c r="V376" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="W376" t="inlineStr">
+        <is>
+          <t>Koffarnus et al. exponentiated model</t>
+        </is>
+      </c>
+      <c r="X376" t="n">
+        <v>1.201</v>
+      </c>
+      <c r="Y376" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z376" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA376" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB376" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC376" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD376" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE376" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF376" t="inlineStr">
+        <is>
+          <t>Omax (maximum expenditure)</t>
+        </is>
+      </c>
+      <c r="AG376" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AH376" t="inlineStr">
+        <is>
+          <t>20 (median)</t>
+        </is>
+      </c>
+      <c r="AI376" t="inlineStr">
+        <is>
+          <t>180 (median)</t>
+        </is>
+      </c>
+      <c r="AJ376" t="inlineStr">
+        <is>
+          <t>60 (median)</t>
+        </is>
+      </c>
+      <c r="AL376" t="inlineStr">
+        <is>
+          <t>Peer-reviewed journal article (Journal of Peking University Health Sciences), not a preprint. Data are baseline responses from a prospective smoking-cessation intervention trial (504 recruited -&gt; 451 valid after removing 53 non-systematic cases -&gt; 447 after excluding 4 non-converging individual fits). All participants male (recruited from coal mining/machinery manufacturing/energy industries in Jiangsu, Inner Mongolia, and Hebei provinces), so no gender reported. Q0/breakpoint/Omax/Pmax in Table 1 are medians (IQR), not means -- reported as such here. Two elasticity figures given: an individual-level log-transformed mean (-2.21 +/- 0.53 SD) and a back-transformed aggregate value (0.54) used for the paper's own smoking-cessation-rate policy simulation; mean_alpha here uses the latter (0.54), consistent with the non-log alpha scale used elsewhere in this index. R2 not reported anywhere in the paper. Paper also fits a smoking-cessation-rate vs. cigarette-price curve (one-phase decay model) using the breakpoint index, estimating a price of at least 37.36 yuan/pack would be needed to reduce mainland China's smoking prevalence to the Healthy China 2030 target of 20% -- out of HPT-index scope, not coded here. First China/CNY entry in the index.</t>
+        </is>
+      </c>
+    </row>
     <row r="377" ht="13" customHeight="1"/>
     <row r="378" ht="13" customHeight="1"/>
     <row r="379" ht="13" customHeight="1"/>

--- a/HPT Resource Index.xlsx
+++ b/HPT Resource Index.xlsx
@@ -610,7 +610,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL376"/>
+  <dimension ref="A1:AL379"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="12.33203125" customWidth="1" min="1" max="1"/>
@@ -72713,9 +72713,513 @@
         </is>
       </c>
     </row>
-    <row r="377" ht="13" customHeight="1"/>
-    <row r="378" ht="13" customHeight="1"/>
-    <row r="379" ht="13" customHeight="1"/>
+    <row r="377" ht="13" customHeight="1">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Lin2025-eco</t>
+        </is>
+      </c>
+      <c r="B377" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>Journal of Hospitality &amp; Tourism Research</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>10.1177/10963480241271307</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1177/10963480241271307</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>Peer-Reviewed</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>Economy hotel room</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>Leisure &amp; Entertainment</t>
+        </is>
+      </c>
+      <c r="J377" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Between-subjects</t>
+        </is>
+      </c>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M377" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N377" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="O377" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="P377" t="n">
+        <v>274</v>
+      </c>
+      <c r="Q377" t="inlineStr">
+        <is>
+          <t>Chinese adults (online panel, Credamo)</t>
+        </is>
+      </c>
+      <c r="R377" t="n">
+        <v>36.46</v>
+      </c>
+      <c r="S377" t="n">
+        <v>13</v>
+      </c>
+      <c r="T377" t="n">
+        <v>0</v>
+      </c>
+      <c r="U377" t="n">
+        <v>1500</v>
+      </c>
+      <c r="V377" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="W377" t="inlineStr">
+        <is>
+          <t>Koffarnus et al. exponentiated model</t>
+        </is>
+      </c>
+      <c r="X377" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Y377" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z377" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA377" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="AB377" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC377" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD377" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE377" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF377" t="inlineStr">
+        <is>
+          <t>Essential Value (EV=5.92); Omax (maximum expenditure, ¥158.0)</t>
+        </is>
+      </c>
+      <c r="AG377" t="n">
+        <v>0.000504</v>
+      </c>
+      <c r="AH377" t="inlineStr">
+        <is>
+          <t>100 (%, purchase probability -- not comparable to other studies' Q0)</t>
+        </is>
+      </c>
+      <c r="AJ377" t="n">
+        <v>495</v>
+      </c>
+      <c r="AK377" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="AL377" t="inlineStr">
+        <is>
+          <t>Peer-reviewed (Journal of Hospitality &amp; Tourism Research, 2025). 3(hotel type) x 2(consumption situation: normal/pandemic) between-subjects HPT experiment, N=822 total valid responses across 6 roughly-equal experimental cells (exact per-cell N only in an online supplement not accessible here -- sample_size below is an estimate, total/3). Demand was measured as PURCHASE PROBABILITY (0-100%), not consumption quantity like the rest of this index -- Q0=100% in every condition (everyone would take a free hotel room with certainty), so Q0 here is not comparable to Q0 elsewhere in the dataset. No breakpoint reported anywhere (the paper's index set is R2/Q0/alpha/EV/Pmax/Omax, not the standard 5-index framework). Essential Value (EV) is this paper's central contribution but has no dedicated numeric column in this schema -- see below for EV alongside Omax. Group demand curves were fit to mean/aggregate data per condition, not per individual. This row: Economy hotels -- the pandemic did not significantly change the demand curve for this tier, so the paper reports one combined value (no averaging needed here).</t>
+        </is>
+      </c>
+    </row>
+    <row r="378" ht="13" customHeight="1">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>Lin2025-mid</t>
+        </is>
+      </c>
+      <c r="B378" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>Journal of Hospitality &amp; Tourism Research</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>10.1177/10963480241271307</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1177/10963480241271307</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>Peer-Reviewed</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>Midscale hotel room</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>Leisure &amp; Entertainment</t>
+        </is>
+      </c>
+      <c r="J378" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Between-subjects</t>
+        </is>
+      </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M378" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N378" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="O378" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="P378" t="n">
+        <v>274</v>
+      </c>
+      <c r="Q378" t="inlineStr">
+        <is>
+          <t>Chinese adults (online panel, Credamo)</t>
+        </is>
+      </c>
+      <c r="R378" t="n">
+        <v>36.46</v>
+      </c>
+      <c r="S378" t="n">
+        <v>13</v>
+      </c>
+      <c r="T378" t="n">
+        <v>0</v>
+      </c>
+      <c r="U378" t="n">
+        <v>2250</v>
+      </c>
+      <c r="V378" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="W378" t="inlineStr">
+        <is>
+          <t>Koffarnus et al. exponentiated model</t>
+        </is>
+      </c>
+      <c r="X378" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Y378" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z378" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA378" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="AB378" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC378" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD378" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE378" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF378" t="inlineStr">
+        <is>
+          <t>Essential Value (EV=9.13); Omax (maximum expenditure, ¥236.0)</t>
+        </is>
+      </c>
+      <c r="AG378" t="n">
+        <v>0.00038</v>
+      </c>
+      <c r="AH378" t="inlineStr">
+        <is>
+          <t>100 (%, purchase probability -- not comparable to other studies' Q0)</t>
+        </is>
+      </c>
+      <c r="AJ378" t="n">
+        <v>747</v>
+      </c>
+      <c r="AK378" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="AL378" t="inlineStr">
+        <is>
+          <t>Peer-reviewed (Journal of Hospitality &amp; Tourism Research, 2025). 3(hotel type) x 2(consumption situation: normal/pandemic) between-subjects HPT experiment, N=822 total valid responses across 6 roughly-equal experimental cells (exact per-cell N only in an online supplement not accessible here -- sample_size below is an estimate, total/3). Demand was measured as PURCHASE PROBABILITY (0-100%), not consumption quantity like the rest of this index -- Q0=100% in every condition (everyone would take a free hotel room with certainty), so Q0 here is not comparable to Q0 elsewhere in the dataset. No breakpoint reported anywhere (the paper's index set is R2/Q0/alpha/EV/Pmax/Omax, not the standard 5-index framework). Essential Value (EV) is this paper's central contribution but has no dedicated numeric column in this schema -- see below for EV alongside Omax. Group demand curves were fit to mean/aggregate data per condition, not per individual. This row: Midscale hotels -- averaged across Normal (R2=0.95, alpha=4.03e-4, EV=8.58, Pmax=702, Omax=222) and Pandemic (R2=0.96, alpha=3.57e-4, EV=9.68, Pmax=792, Omax=250) conditions, which the paper found significantly different (pandemic made demand more inelastic) -- averaging obscures that finding; see the paper for the real per-condition values.</t>
+        </is>
+      </c>
+    </row>
+    <row r="379" ht="13" customHeight="1">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>Lin2025-ups</t>
+        </is>
+      </c>
+      <c r="B379" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>Journal of Hospitality &amp; Tourism Research</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>10.1177/10963480241271307</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1177/10963480241271307</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>Peer-Reviewed</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>Upscale hotel room</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>Leisure &amp; Entertainment</t>
+        </is>
+      </c>
+      <c r="J379" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Between-subjects</t>
+        </is>
+      </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M379" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N379" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="O379" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="P379" t="n">
+        <v>274</v>
+      </c>
+      <c r="Q379" t="inlineStr">
+        <is>
+          <t>Chinese adults (online panel, Credamo)</t>
+        </is>
+      </c>
+      <c r="R379" t="n">
+        <v>36.46</v>
+      </c>
+      <c r="S379" t="n">
+        <v>13</v>
+      </c>
+      <c r="T379" t="n">
+        <v>0</v>
+      </c>
+      <c r="U379" t="n">
+        <v>3000</v>
+      </c>
+      <c r="V379" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="W379" t="inlineStr">
+        <is>
+          <t>Koffarnus et al. exponentiated model</t>
+        </is>
+      </c>
+      <c r="X379" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Y379" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z379" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA379" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="AB379" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC379" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD379" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE379" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF379" t="inlineStr">
+        <is>
+          <t>Essential Value (EV=21.00); Omax (maximum expenditure, ¥503.5)</t>
+        </is>
+      </c>
+      <c r="AG379" t="n">
+        <v>0.000238</v>
+      </c>
+      <c r="AH379" t="inlineStr">
+        <is>
+          <t>100 (%, purchase probability -- not comparable to other studies' Q0)</t>
+        </is>
+      </c>
+      <c r="AJ379" t="n">
+        <v>1642.5</v>
+      </c>
+      <c r="AK379" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="AL379" t="inlineStr">
+        <is>
+          <t>Peer-reviewed (Journal of Hospitality &amp; Tourism Research, 2025). 3(hotel type) x 2(consumption situation: normal/pandemic) between-subjects HPT experiment, N=822 total valid responses across 6 roughly-equal experimental cells (exact per-cell N only in an online supplement not accessible here -- sample_size below is an estimate, total/3). Demand was measured as PURCHASE PROBABILITY (0-100%), not consumption quantity like the rest of this index -- Q0=100% in every condition (everyone would take a free hotel room with certainty), so Q0 here is not comparable to Q0 elsewhere in the dataset. No breakpoint reported anywhere (the paper's index set is R2/Q0/alpha/EV/Pmax/Omax, not the standard 5-index framework). Essential Value (EV) is this paper's central contribution but has no dedicated numeric column in this schema -- see below for EV alongside Omax. Group demand curves were fit to mean/aggregate data per condition, not per individual. This row: Upscale hotels -- averaged across Normal (R2=0.96, alpha=2.21e-4, EV=22.48, Pmax=1758, Omax=539) and Pandemic (R2=0.97, alpha=2.55e-4, EV=19.52, Pmax=1527, Omax=468) conditions, which the paper found significantly different (pandemic made demand more elastic) -- averaging obscures that finding; see the paper for the real per-condition values.</t>
+        </is>
+      </c>
+    </row>
     <row r="380" ht="13" customHeight="1"/>
     <row r="381" ht="13" customHeight="1"/>
     <row r="382" ht="13" customHeight="1"/>

--- a/HPT Resource Index.xlsx
+++ b/HPT Resource Index.xlsx
@@ -610,7 +610,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL379"/>
+  <dimension ref="A1:AL381"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="12.33203125" customWidth="1" min="1" max="1"/>
@@ -73220,8 +73220,322 @@
         </is>
       </c>
     </row>
-    <row r="380" ht="13" customHeight="1"/>
-    <row r="381" ht="13" customHeight="1"/>
+    <row r="380" ht="13" customHeight="1">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Tewogbola2023-covid</t>
+        </is>
+      </c>
+      <c r="B380" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>medRxiv (preprint)</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>10.1101/2023.07.24.23293101</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>https://www.medrxiv.org/content/10.1101/2023.07.24.23293101v1</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>Preprint</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>COVID-19 vaccine</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>Health &amp; Prevention</t>
+        </is>
+      </c>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M380" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N380" t="inlineStr">
+        <is>
+          <t>Nigeria; United States</t>
+        </is>
+      </c>
+      <c r="O380" t="inlineStr">
+        <is>
+          <t>Multi-regional</t>
+        </is>
+      </c>
+      <c r="P380" t="n">
+        <v>109</v>
+      </c>
+      <c r="Q380" t="inlineStr">
+        <is>
+          <t>Mixed community sample (US MTurk workers; Nigerian social media-recruited adults)</t>
+        </is>
+      </c>
+      <c r="S380" t="n">
+        <v>11</v>
+      </c>
+      <c r="T380" t="n">
+        <v>0</v>
+      </c>
+      <c r="U380" t="n">
+        <v>1</v>
+      </c>
+      <c r="V380" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W380" t="inlineStr">
+        <is>
+          <t>Hursh &amp; Silberberg exponential model</t>
+        </is>
+      </c>
+      <c r="X380" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Y380" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z380" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA380" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="AB380" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC380" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD380" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE380" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AH380" t="inlineStr">
+        <is>
+          <t>91.2 (%, purchase probability -- not comparable to other studies' Q0)</t>
+        </is>
+      </c>
+      <c r="AJ380" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AK380" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AL380" t="inlineStr">
+        <is>
+          <t>Self-authored by the PI (PROMISE Labs Africa), with Eric A. Jacobs and Justin T. McDaniel (SIU Carbondale). medRxiv preprint, not yet peer-reviewed. N=109 (65 Nigeria, 44 USA); vaccine type (COVID-19/HIV) was within-subjects (same participants rated both), country was between-subjects. Pooled across country here (using Figure 2a's own cross-country aggregate values) -- this obscures the paper's actual key finding, a significant country x vaccine-type interaction (Nigerian participants showed higher demand for the HIV vaccine than COVID-19; American participants showed the reverse); see the paper for the real per-country values. "Price" is hospitalization risk from the vaccine (0=no risk, 1=certain hospitalization), substituted for a monetary price -- lowest_price/highest_price represent that probability scale, not currency. Q0 is measured as purchase-probability (0-100%), not consumption quantity -- not comparable to Q0 elsewhere in this index. No single aggregate alpha value is stated in the text (only shown per-individual for the 10 best-fitting curves per vaccine in Table 1), so mean_alpha is left blank rather than guessed. No breakpoint or essential value reported, despite essential value being discussed conceptually in the introduction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="381" ht="13" customHeight="1">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Tewogbola2023-hiv</t>
+        </is>
+      </c>
+      <c r="B381" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>medRxiv (preprint)</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>10.1101/2023.07.24.23293101</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>https://www.medrxiv.org/content/10.1101/2023.07.24.23293101v1</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>Preprint</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>HIV vaccine</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>Health &amp; Prevention</t>
+        </is>
+      </c>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M381" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N381" t="inlineStr">
+        <is>
+          <t>Nigeria; United States</t>
+        </is>
+      </c>
+      <c r="O381" t="inlineStr">
+        <is>
+          <t>Multi-regional</t>
+        </is>
+      </c>
+      <c r="P381" t="n">
+        <v>109</v>
+      </c>
+      <c r="Q381" t="inlineStr">
+        <is>
+          <t>Mixed community sample (US MTurk workers; Nigerian social media-recruited adults)</t>
+        </is>
+      </c>
+      <c r="S381" t="n">
+        <v>11</v>
+      </c>
+      <c r="T381" t="n">
+        <v>0</v>
+      </c>
+      <c r="U381" t="n">
+        <v>1</v>
+      </c>
+      <c r="V381" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W381" t="inlineStr">
+        <is>
+          <t>Hursh &amp; Silberberg exponential model</t>
+        </is>
+      </c>
+      <c r="X381" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Y381" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z381" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA381" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="AB381" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC381" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD381" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE381" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AH381" t="inlineStr">
+        <is>
+          <t>92.4 (%, purchase probability -- not comparable to other studies' Q0)</t>
+        </is>
+      </c>
+      <c r="AJ381" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AK381" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AL381" t="inlineStr">
+        <is>
+          <t>Self-authored by the PI (PROMISE Labs Africa), with Eric A. Jacobs and Justin T. McDaniel (SIU Carbondale). medRxiv preprint, not yet peer-reviewed. N=109 (65 Nigeria, 44 USA); vaccine type (COVID-19/HIV) was within-subjects (same participants rated both), country was between-subjects. Pooled across country here (using Figure 2a's own cross-country aggregate values) -- this obscures the paper's actual key finding, a significant country x vaccine-type interaction (Nigerian participants showed higher demand for the HIV vaccine than COVID-19; American participants showed the reverse); see the paper for the real per-country values. "Price" is hospitalization risk from the vaccine (0=no risk, 1=certain hospitalization), substituted for a monetary price -- lowest_price/highest_price represent that probability scale, not currency. Q0 is measured as purchase-probability (0-100%), not consumption quantity -- not comparable to Q0 elsewhere in this index. No single aggregate alpha value is stated in the text (only shown per-individual for the 10 best-fitting curves per vaccine in Table 1), so mean_alpha is left blank rather than guessed. No breakpoint or essential value reported, despite essential value being discussed conceptually in the introduction.</t>
+        </is>
+      </c>
+    </row>
     <row r="382" ht="13" customHeight="1"/>
     <row r="383" ht="13" customHeight="1"/>
     <row r="384" ht="13" customHeight="1"/>

--- a/HPT Resource Index.xlsx
+++ b/HPT Resource Index.xlsx
@@ -610,7 +610,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL381"/>
+  <dimension ref="A1:AL391"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="12.33203125" customWidth="1" min="1" max="1"/>
@@ -73536,16 +73536,1656 @@
         </is>
       </c>
     </row>
-    <row r="382" ht="13" customHeight="1"/>
-    <row r="383" ht="13" customHeight="1"/>
-    <row r="384" ht="13" customHeight="1"/>
-    <row r="385" ht="13" customHeight="1"/>
-    <row r="386" ht="13" customHeight="1"/>
-    <row r="387" ht="13" customHeight="1"/>
-    <row r="388" ht="13" customHeight="1"/>
-    <row r="389" ht="13" customHeight="1"/>
-    <row r="390" ht="13" customHeight="1"/>
-    <row r="391" ht="13" customHeight="1"/>
+    <row r="382" ht="13" customHeight="1">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Tewogbola2025-hiv-e1</t>
+        </is>
+      </c>
+      <c r="B382" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>Journal of the Experimental Analysis of Behavior</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>10.1002/jeab.70038</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/jeab.70038</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>Peer-Reviewed</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>HIV vaccine</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>Health &amp; Prevention</t>
+        </is>
+      </c>
+      <c r="J382" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>Between-subjects</t>
+        </is>
+      </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M382" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N382" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="O382" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="P382" t="n">
+        <v>285</v>
+      </c>
+      <c r="Q382" t="inlineStr">
+        <is>
+          <t>Sexual and gender minority adults (Reddit- and LGBTQ+ community organization-recruited)</t>
+        </is>
+      </c>
+      <c r="R382" t="n">
+        <v>29.37</v>
+      </c>
+      <c r="S382" t="n">
+        <v>15</v>
+      </c>
+      <c r="T382" t="n">
+        <v>0</v>
+      </c>
+      <c r="U382" t="n">
+        <v>2000</v>
+      </c>
+      <c r="V382" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="W382" t="inlineStr">
+        <is>
+          <t>Koffarnus et al. exponentiated model</t>
+        </is>
+      </c>
+      <c r="X382" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Y382" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z382" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA382" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="AB382" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC382" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD382" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE382" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG382" t="n">
+        <v>6.397e-06</v>
+      </c>
+      <c r="AH382" t="n">
+        <v>70.33</v>
+      </c>
+      <c r="AI382" t="n">
+        <v>522.33</v>
+      </c>
+      <c r="AJ382" t="n">
+        <v>434.16</v>
+      </c>
+      <c r="AK382" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="AL382" t="inlineStr">
+        <is>
+          <t>Self-authored by the PI (PROMISE Labs Africa), with Eric A. Jacobs, Yueh-Ting Lee, and Ryan N. Redner (SIU Carbondale School of Psychological and Behavioral Sciences), Justin T. McDaniel (SIU School of Health Sciences), and Jebaraj Asirvatham (SIU School of Agricultural Sciences). Peer-reviewed (Journal of the Experimental Analysis of Behavior, 2025). Open-access status not confirmed -- no CC license visible on the article pages reviewed here, so marked No pending verification. Both experiments used the same 393 recruited sexual/gender-minority participants (Reddit + LGBTQ+ community organizations, U.S., aged 19+); Experiment 1 retained N=285 after exclusions, Experiment 2 retained N=236 (all Experiment-1 completers were invited into Experiment 2). 15 price points, $0-$2,000, VAS-slider purchase-likelihood task adapted from Hursh et al. (2020). This row: Experiment 1 (N=285), participants randomized to 9 groups crossing vaccine administration mode (oral/mucosal/subcutaneous) x perceived dosage (one dose/two doses/annual dose). The paper's key finding was that these vaccine-characteristic manipulations had minimal effect on demand (regression R²=.007 for Q0, R²=.001 for log alpha, both ns after Bonferroni correction -- see Table 3); individual factors (injection drug use history, experienced racial discrimination, prior vaccine uptake, trust in science/government, low household income) were the significant predictors instead. Because condition had so little effect, and the paper did not report a single pooled aggregate across all 9 cells (only the 3 mode-marginal and 3 dosage-marginal aggregates in Table 2, which are two different collapses of the same 285 participants), this row is the simple mean of those 6 marginal Q0/alpha/Pmax/breakpoint/R² values as an approximation of the overall aggregate -- see Table 2 for the real per-condition breakdown. Experiment 2 (bundling) is entered as 9 separate rows below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="383" ht="13" customHeight="1">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Tewogbola2025-hiv-prep</t>
+        </is>
+      </c>
+      <c r="B383" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>Journal of the Experimental Analysis of Behavior</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>10.1002/jeab.70038</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/jeab.70038</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>Peer-Reviewed</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>HIV vaccine</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>Health &amp; Prevention</t>
+        </is>
+      </c>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Between-subjects</t>
+        </is>
+      </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M383" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N383" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="O383" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="P383" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q383" t="inlineStr">
+        <is>
+          <t>Sexual and gender minority adults (Reddit- and LGBTQ+ community organization-recruited)</t>
+        </is>
+      </c>
+      <c r="R383" t="n">
+        <v>29.37</v>
+      </c>
+      <c r="S383" t="n">
+        <v>15</v>
+      </c>
+      <c r="T383" t="n">
+        <v>0</v>
+      </c>
+      <c r="U383" t="n">
+        <v>2000</v>
+      </c>
+      <c r="V383" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="W383" t="inlineStr">
+        <is>
+          <t>Koffarnus et al. exponentiated model</t>
+        </is>
+      </c>
+      <c r="X383" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Y383" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z383" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA383" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="AB383" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC383" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD383" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE383" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG383" t="n">
+        <v>6.93e-06</v>
+      </c>
+      <c r="AH383" t="n">
+        <v>71.51000000000001</v>
+      </c>
+      <c r="AI383" t="n">
+        <v>621</v>
+      </c>
+      <c r="AJ383" t="n">
+        <v>380.66</v>
+      </c>
+      <c r="AK383" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AL383" t="inlineStr">
+        <is>
+          <t>Self-authored by the PI (PROMISE Labs Africa), with Eric A. Jacobs, Yueh-Ting Lee, and Ryan N. Redner (SIU Carbondale School of Psychological and Behavioral Sciences), Justin T. McDaniel (SIU School of Health Sciences), and Jebaraj Asirvatham (SIU School of Agricultural Sciences). Peer-reviewed (Journal of the Experimental Analysis of Behavior, 2025). Open-access status not confirmed -- no CC license visible on the article pages reviewed here, so marked No pending verification. Both experiments used the same 393 recruited sexual/gender-minority participants (Reddit + LGBTQ+ community organizations, U.S., aged 19+); Experiment 1 retained N=285 after exclusions, Experiment 2 retained N=236 (all Experiment-1 completers were invited into Experiment 2). 15 price points, $0-$2,000, VAS-slider purchase-likelihood task adapted from Hursh et al. (2020). This row: Experiment 2 (bundle-condition n=24 of N=236 total; Table 4's 9 per-bundle n's sum to 235, one short of the stated 236 -- discrepancy in the source, not corrected here), demand for a hypothetical HIV vaccine bundled with PrEP, values from Table 5. Bundling effects were subtle overall across the 9 conditions (Q0 R²=.016, log alpha R²=.104 -- see Table 6), smaller than the effect of individual factors (Q0 R²=.40, log alpha R²=.32 -- see Table 6 Model 2). This is the reference condition in Table 6's regression models.</t>
+        </is>
+      </c>
+    </row>
+    <row r="384" ht="13" customHeight="1">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Tewogbola2025-hiv-hivtest</t>
+        </is>
+      </c>
+      <c r="B384" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>Journal of the Experimental Analysis of Behavior</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>10.1002/jeab.70038</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/jeab.70038</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>Peer-Reviewed</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>HIV vaccine</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>Health &amp; Prevention</t>
+        </is>
+      </c>
+      <c r="J384" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Between-subjects</t>
+        </is>
+      </c>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M384" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N384" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="O384" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="P384" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q384" t="inlineStr">
+        <is>
+          <t>Sexual and gender minority adults (Reddit- and LGBTQ+ community organization-recruited)</t>
+        </is>
+      </c>
+      <c r="R384" t="n">
+        <v>29.37</v>
+      </c>
+      <c r="S384" t="n">
+        <v>15</v>
+      </c>
+      <c r="T384" t="n">
+        <v>0</v>
+      </c>
+      <c r="U384" t="n">
+        <v>2000</v>
+      </c>
+      <c r="V384" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="W384" t="inlineStr">
+        <is>
+          <t>Koffarnus et al. exponentiated model</t>
+        </is>
+      </c>
+      <c r="X384" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Y384" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z384" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA384" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="AB384" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC384" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD384" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE384" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG384" t="n">
+        <v>8.16e-06</v>
+      </c>
+      <c r="AH384" t="n">
+        <v>81.62</v>
+      </c>
+      <c r="AI384" t="n">
+        <v>462</v>
+      </c>
+      <c r="AJ384" t="n">
+        <v>261.83</v>
+      </c>
+      <c r="AK384" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="AL384" t="inlineStr">
+        <is>
+          <t>Self-authored by the PI (PROMISE Labs Africa), with Eric A. Jacobs, Yueh-Ting Lee, and Ryan N. Redner (SIU Carbondale School of Psychological and Behavioral Sciences), Justin T. McDaniel (SIU School of Health Sciences), and Jebaraj Asirvatham (SIU School of Agricultural Sciences). Peer-reviewed (Journal of the Experimental Analysis of Behavior, 2025). Open-access status not confirmed -- no CC license visible on the article pages reviewed here, so marked No pending verification. Both experiments used the same 393 recruited sexual/gender-minority participants (Reddit + LGBTQ+ community organizations, U.S., aged 19+); Experiment 1 retained N=285 after exclusions, Experiment 2 retained N=236 (all Experiment-1 completers were invited into Experiment 2). 15 price points, $0-$2,000, VAS-slider purchase-likelihood task adapted from Hursh et al. (2020). This row: Experiment 2 (bundle-condition n=26 of N=236 total; Table 4's 9 per-bundle n's sum to 235, one short of the stated 236 -- discrepancy in the source, not corrected here), demand for a hypothetical HIV vaccine bundled with an HIV test kit, values from Table 5. Bundling effects were subtle overall across the 9 conditions (Q0 R²=.016, log alpha R²=.104 -- see Table 6), smaller than the effect of individual factors (Q0 R²=.40, log alpha R²=.32 -- see Table 6 Model 2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="385" ht="13" customHeight="1">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Tewogbola2025-hiv-condoms</t>
+        </is>
+      </c>
+      <c r="B385" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>Journal of the Experimental Analysis of Behavior</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>10.1002/jeab.70038</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/jeab.70038</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>Peer-Reviewed</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>HIV vaccine</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>Health &amp; Prevention</t>
+        </is>
+      </c>
+      <c r="J385" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Between-subjects</t>
+        </is>
+      </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M385" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N385" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="O385" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="P385" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q385" t="inlineStr">
+        <is>
+          <t>Sexual and gender minority adults (Reddit- and LGBTQ+ community organization-recruited)</t>
+        </is>
+      </c>
+      <c r="R385" t="n">
+        <v>29.37</v>
+      </c>
+      <c r="S385" t="n">
+        <v>15</v>
+      </c>
+      <c r="T385" t="n">
+        <v>0</v>
+      </c>
+      <c r="U385" t="n">
+        <v>2000</v>
+      </c>
+      <c r="V385" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="W385" t="inlineStr">
+        <is>
+          <t>Koffarnus et al. exponentiated model</t>
+        </is>
+      </c>
+      <c r="X385" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Y385" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z385" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA385" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="AB385" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC385" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD385" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE385" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG385" t="n">
+        <v>5.2e-06</v>
+      </c>
+      <c r="AH385" t="n">
+        <v>68.45999999999999</v>
+      </c>
+      <c r="AI385" t="n">
+        <v>502</v>
+      </c>
+      <c r="AJ385" t="n">
+        <v>530.03</v>
+      </c>
+      <c r="AK385" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AL385" t="inlineStr">
+        <is>
+          <t>Self-authored by the PI (PROMISE Labs Africa), with Eric A. Jacobs, Yueh-Ting Lee, and Ryan N. Redner (SIU Carbondale School of Psychological and Behavioral Sciences), Justin T. McDaniel (SIU School of Health Sciences), and Jebaraj Asirvatham (SIU School of Agricultural Sciences). Peer-reviewed (Journal of the Experimental Analysis of Behavior, 2025). Open-access status not confirmed -- no CC license visible on the article pages reviewed here, so marked No pending verification. Both experiments used the same 393 recruited sexual/gender-minority participants (Reddit + LGBTQ+ community organizations, U.S., aged 19+); Experiment 1 retained N=285 after exclusions, Experiment 2 retained N=236 (all Experiment-1 completers were invited into Experiment 2). 15 price points, $0-$2,000, VAS-slider purchase-likelihood task adapted from Hursh et al. (2020). This row: Experiment 2 (bundle-condition n=27 of N=236 total; Table 4's 9 per-bundle n's sum to 235, one short of the stated 236 -- discrepancy in the source, not corrected here), demand for a hypothetical HIV vaccine bundled with condoms, values from Table 5. Bundling effects were subtle overall across the 9 conditions (Q0 R²=.016, log alpha R²=.104 -- see Table 6), smaller than the effect of individual factors (Q0 R²=.40, log alpha R²=.32 -- see Table 6 Model 2). Log alpha differed significantly from the PrEP-bundle reference before correction (β=0.91, p=.02) -- higher price sensitivity, interpreted as possible perceived redundancy with condoms as HIV prevention -- but not after Bonferroni correction (adjusted p&lt;.005; see Table 6).</t>
+        </is>
+      </c>
+    </row>
+    <row r="386" ht="13" customHeight="1">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Tewogbola2025-hiv-covid</t>
+        </is>
+      </c>
+      <c r="B386" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>Journal of the Experimental Analysis of Behavior</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>10.1002/jeab.70038</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/jeab.70038</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>Peer-Reviewed</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>HIV vaccine</t>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>Health &amp; Prevention</t>
+        </is>
+      </c>
+      <c r="J386" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Between-subjects</t>
+        </is>
+      </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M386" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N386" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="O386" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="P386" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q386" t="inlineStr">
+        <is>
+          <t>Sexual and gender minority adults (Reddit- and LGBTQ+ community organization-recruited)</t>
+        </is>
+      </c>
+      <c r="R386" t="n">
+        <v>29.37</v>
+      </c>
+      <c r="S386" t="n">
+        <v>15</v>
+      </c>
+      <c r="T386" t="n">
+        <v>0</v>
+      </c>
+      <c r="U386" t="n">
+        <v>2000</v>
+      </c>
+      <c r="V386" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="W386" t="inlineStr">
+        <is>
+          <t>Koffarnus et al. exponentiated model</t>
+        </is>
+      </c>
+      <c r="X386" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Y386" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z386" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA386" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="AB386" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC386" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD386" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE386" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG386" t="n">
+        <v>7.849999999999999e-06</v>
+      </c>
+      <c r="AH386" t="n">
+        <v>76.73999999999999</v>
+      </c>
+      <c r="AI386" t="n">
+        <v>504</v>
+      </c>
+      <c r="AJ386" t="n">
+        <v>313.27</v>
+      </c>
+      <c r="AK386" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AL386" t="inlineStr">
+        <is>
+          <t>Self-authored by the PI (PROMISE Labs Africa), with Eric A. Jacobs, Yueh-Ting Lee, and Ryan N. Redner (SIU Carbondale School of Psychological and Behavioral Sciences), Justin T. McDaniel (SIU School of Health Sciences), and Jebaraj Asirvatham (SIU School of Agricultural Sciences). Peer-reviewed (Journal of the Experimental Analysis of Behavior, 2025). Open-access status not confirmed -- no CC license visible on the article pages reviewed here, so marked No pending verification. Both experiments used the same 393 recruited sexual/gender-minority participants (Reddit + LGBTQ+ community organizations, U.S., aged 19+); Experiment 1 retained N=285 after exclusions, Experiment 2 retained N=236 (all Experiment-1 completers were invited into Experiment 2). 15 price points, $0-$2,000, VAS-slider purchase-likelihood task adapted from Hursh et al. (2020). This row: Experiment 2 (bundle-condition n=27 of N=236 total; Table 4's 9 per-bundle n's sum to 235, one short of the stated 236 -- discrepancy in the source, not corrected here), demand for a hypothetical HIV vaccine bundled with a COVID-19 vaccine, values from Table 5. Bundling effects were subtle overall across the 9 conditions (Q0 R²=.016, log alpha R²=.104 -- see Table 6), smaller than the effect of individual factors (Q0 R²=.40, log alpha R²=.32 -- see Table 6 Model 2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="387" ht="13" customHeight="1">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Tewogbola2025-hiv-flu</t>
+        </is>
+      </c>
+      <c r="B387" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>Journal of the Experimental Analysis of Behavior</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>10.1002/jeab.70038</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/jeab.70038</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>Peer-Reviewed</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>HIV vaccine</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>Health &amp; Prevention</t>
+        </is>
+      </c>
+      <c r="J387" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Between-subjects</t>
+        </is>
+      </c>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M387" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N387" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="O387" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="P387" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q387" t="inlineStr">
+        <is>
+          <t>Sexual and gender minority adults (Reddit- and LGBTQ+ community organization-recruited)</t>
+        </is>
+      </c>
+      <c r="R387" t="n">
+        <v>29.37</v>
+      </c>
+      <c r="S387" t="n">
+        <v>15</v>
+      </c>
+      <c r="T387" t="n">
+        <v>0</v>
+      </c>
+      <c r="U387" t="n">
+        <v>2000</v>
+      </c>
+      <c r="V387" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="W387" t="inlineStr">
+        <is>
+          <t>Koffarnus et al. exponentiated model</t>
+        </is>
+      </c>
+      <c r="X387" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Y387" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z387" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA387" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="AB387" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC387" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD387" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE387" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG387" t="n">
+        <v>5.56e-06</v>
+      </c>
+      <c r="AH387" t="n">
+        <v>65.59</v>
+      </c>
+      <c r="AI387" t="n">
+        <v>573</v>
+      </c>
+      <c r="AJ387" t="n">
+        <v>517.85</v>
+      </c>
+      <c r="AK387" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AL387" t="inlineStr">
+        <is>
+          <t>Self-authored by the PI (PROMISE Labs Africa), with Eric A. Jacobs, Yueh-Ting Lee, and Ryan N. Redner (SIU Carbondale School of Psychological and Behavioral Sciences), Justin T. McDaniel (SIU School of Health Sciences), and Jebaraj Asirvatham (SIU School of Agricultural Sciences). Peer-reviewed (Journal of the Experimental Analysis of Behavior, 2025). Open-access status not confirmed -- no CC license visible on the article pages reviewed here, so marked No pending verification. Both experiments used the same 393 recruited sexual/gender-minority participants (Reddit + LGBTQ+ community organizations, U.S., aged 19+); Experiment 1 retained N=285 after exclusions, Experiment 2 retained N=236 (all Experiment-1 completers were invited into Experiment 2). 15 price points, $0-$2,000, VAS-slider purchase-likelihood task adapted from Hursh et al. (2020). This row: Experiment 2 (bundle-condition n=27 of N=236 total; Table 4's 9 per-bundle n's sum to 235, one short of the stated 236 -- discrepancy in the source, not corrected here), demand for a hypothetical HIV vaccine bundled with a flu vaccine, values from Table 5. Bundling effects were subtle overall across the 9 conditions (Q0 R²=.016, log alpha R²=.104 -- see Table 6), smaller than the effect of individual factors (Q0 R²=.40, log alpha R²=.32 -- see Table 6 Model 2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="388" ht="13" customHeight="1">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Tewogbola2025-hiv-hpv</t>
+        </is>
+      </c>
+      <c r="B388" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>Journal of the Experimental Analysis of Behavior</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>10.1002/jeab.70038</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/jeab.70038</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>Peer-Reviewed</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>HIV vaccine</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>Health &amp; Prevention</t>
+        </is>
+      </c>
+      <c r="J388" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Between-subjects</t>
+        </is>
+      </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M388" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N388" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="O388" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="P388" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q388" t="inlineStr">
+        <is>
+          <t>Sexual and gender minority adults (Reddit- and LGBTQ+ community organization-recruited)</t>
+        </is>
+      </c>
+      <c r="R388" t="n">
+        <v>29.37</v>
+      </c>
+      <c r="S388" t="n">
+        <v>15</v>
+      </c>
+      <c r="T388" t="n">
+        <v>0</v>
+      </c>
+      <c r="U388" t="n">
+        <v>2000</v>
+      </c>
+      <c r="V388" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="W388" t="inlineStr">
+        <is>
+          <t>Koffarnus et al. exponentiated model</t>
+        </is>
+      </c>
+      <c r="X388" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Y388" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z388" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA388" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="AB388" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC388" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD388" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE388" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG388" t="n">
+        <v>5.77e-06</v>
+      </c>
+      <c r="AH388" t="n">
+        <v>81.44</v>
+      </c>
+      <c r="AI388" t="n">
+        <v>501</v>
+      </c>
+      <c r="AJ388" t="n">
+        <v>401.66</v>
+      </c>
+      <c r="AK388" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AL388" t="inlineStr">
+        <is>
+          <t>Self-authored by the PI (PROMISE Labs Africa), with Eric A. Jacobs, Yueh-Ting Lee, and Ryan N. Redner (SIU Carbondale School of Psychological and Behavioral Sciences), Justin T. McDaniel (SIU School of Health Sciences), and Jebaraj Asirvatham (SIU School of Agricultural Sciences). Peer-reviewed (Journal of the Experimental Analysis of Behavior, 2025). Open-access status not confirmed -- no CC license visible on the article pages reviewed here, so marked No pending verification. Both experiments used the same 393 recruited sexual/gender-minority participants (Reddit + LGBTQ+ community organizations, U.S., aged 19+); Experiment 1 retained N=285 after exclusions, Experiment 2 retained N=236 (all Experiment-1 completers were invited into Experiment 2). 15 price points, $0-$2,000, VAS-slider purchase-likelihood task adapted from Hursh et al. (2020). This row: Experiment 2 (bundle-condition n=26 of N=236 total; Table 4's 9 per-bundle n's sum to 235, one short of the stated 236 -- discrepancy in the source, not corrected here), demand for a hypothetical HIV vaccine bundled with an HPV vaccine, values from Table 5. Bundling effects were subtle overall across the 9 conditions (Q0 R²=.016, log alpha R²=.104 -- see Table 6), smaller than the effect of individual factors (Q0 R²=.40, log alpha R²=.32 -- see Table 6 Model 2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="389" ht="13" customHeight="1">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>Tewogbola2025-hiv-dental</t>
+        </is>
+      </c>
+      <c r="B389" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>Journal of the Experimental Analysis of Behavior</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>10.1002/jeab.70038</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/jeab.70038</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>Peer-Reviewed</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>HIV vaccine</t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>Health &amp; Prevention</t>
+        </is>
+      </c>
+      <c r="J389" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Between-subjects</t>
+        </is>
+      </c>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M389" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N389" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="O389" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="P389" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q389" t="inlineStr">
+        <is>
+          <t>Sexual and gender minority adults (Reddit- and LGBTQ+ community organization-recruited)</t>
+        </is>
+      </c>
+      <c r="R389" t="n">
+        <v>29.37</v>
+      </c>
+      <c r="S389" t="n">
+        <v>15</v>
+      </c>
+      <c r="T389" t="n">
+        <v>0</v>
+      </c>
+      <c r="U389" t="n">
+        <v>2000</v>
+      </c>
+      <c r="V389" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="W389" t="inlineStr">
+        <is>
+          <t>Koffarnus et al. exponentiated model</t>
+        </is>
+      </c>
+      <c r="X389" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Y389" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z389" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA389" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="AB389" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC389" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD389" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE389" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG389" t="n">
+        <v>4.65e-06</v>
+      </c>
+      <c r="AH389" t="n">
+        <v>68.09999999999999</v>
+      </c>
+      <c r="AI389" t="n">
+        <v>763</v>
+      </c>
+      <c r="AJ389" t="n">
+        <v>595.51</v>
+      </c>
+      <c r="AK389" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AL389" t="inlineStr">
+        <is>
+          <t>Self-authored by the PI (PROMISE Labs Africa), with Eric A. Jacobs, Yueh-Ting Lee, and Ryan N. Redner (SIU Carbondale School of Psychological and Behavioral Sciences), Justin T. McDaniel (SIU School of Health Sciences), and Jebaraj Asirvatham (SIU School of Agricultural Sciences). Peer-reviewed (Journal of the Experimental Analysis of Behavior, 2025). Open-access status not confirmed -- no CC license visible on the article pages reviewed here, so marked No pending verification. Both experiments used the same 393 recruited sexual/gender-minority participants (Reddit + LGBTQ+ community organizations, U.S., aged 19+); Experiment 1 retained N=285 after exclusions, Experiment 2 retained N=236 (all Experiment-1 completers were invited into Experiment 2). 15 price points, $0-$2,000, VAS-slider purchase-likelihood task adapted from Hursh et al. (2020). This row: Experiment 2 (bundle-condition n=28 of N=236 total; Table 4's 9 per-bundle n's sum to 235, one short of the stated 236 -- discrepancy in the source, not corrected here), demand for a hypothetical HIV vaccine bundled with a free dental examination, values from Table 5. Bundling effects were subtle overall across the 9 conditions (Q0 R²=.016, log alpha R²=.104 -- see Table 6), smaller than the effect of individual factors (Q0 R²=.40, log alpha R²=.32 -- see Table 6 Model 2). Log alpha differed significantly from the PrEP-bundle reference before correction (β=0.78, p=.04) -- higher price sensitivity, interpreted as possible perceived low relevance of dental care to HIV prevention -- but not after Bonferroni correction (adjusted p&lt;.005; see Table 6).</t>
+        </is>
+      </c>
+    </row>
+    <row r="390" ht="13" customHeight="1">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Tewogbola2025-hiv-eye</t>
+        </is>
+      </c>
+      <c r="B390" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>Journal of the Experimental Analysis of Behavior</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>10.1002/jeab.70038</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/jeab.70038</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>Peer-Reviewed</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>HIV vaccine</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>Health &amp; Prevention</t>
+        </is>
+      </c>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Between-subjects</t>
+        </is>
+      </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M390" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N390" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="O390" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="P390" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q390" t="inlineStr">
+        <is>
+          <t>Sexual and gender minority adults (Reddit- and LGBTQ+ community organization-recruited)</t>
+        </is>
+      </c>
+      <c r="R390" t="n">
+        <v>29.37</v>
+      </c>
+      <c r="S390" t="n">
+        <v>15</v>
+      </c>
+      <c r="T390" t="n">
+        <v>0</v>
+      </c>
+      <c r="U390" t="n">
+        <v>2000</v>
+      </c>
+      <c r="V390" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="W390" t="inlineStr">
+        <is>
+          <t>Koffarnus et al. exponentiated model</t>
+        </is>
+      </c>
+      <c r="X390" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Y390" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z390" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA390" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="AB390" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC390" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD390" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE390" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG390" t="n">
+        <v>7.82e-06</v>
+      </c>
+      <c r="AH390" t="n">
+        <v>81.52</v>
+      </c>
+      <c r="AI390" t="n">
+        <v>458</v>
+      </c>
+      <c r="AJ390" t="n">
+        <v>296.15</v>
+      </c>
+      <c r="AK390" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AL390" t="inlineStr">
+        <is>
+          <t>Self-authored by the PI (PROMISE Labs Africa), with Eric A. Jacobs, Yueh-Ting Lee, and Ryan N. Redner (SIU Carbondale School of Psychological and Behavioral Sciences), Justin T. McDaniel (SIU School of Health Sciences), and Jebaraj Asirvatham (SIU School of Agricultural Sciences). Peer-reviewed (Journal of the Experimental Analysis of Behavior, 2025). Open-access status not confirmed -- no CC license visible on the article pages reviewed here, so marked No pending verification. Both experiments used the same 393 recruited sexual/gender-minority participants (Reddit + LGBTQ+ community organizations, U.S., aged 19+); Experiment 1 retained N=285 after exclusions, Experiment 2 retained N=236 (all Experiment-1 completers were invited into Experiment 2). 15 price points, $0-$2,000, VAS-slider purchase-likelihood task adapted from Hursh et al. (2020). This row: Experiment 2 (bundle-condition n=25 of N=236 total; Table 4's 9 per-bundle n's sum to 235, one short of the stated 236 -- discrepancy in the source, not corrected here), demand for a hypothetical HIV vaccine bundled with a free eye examination, values from Table 5. Bundling effects were subtle overall across the 9 conditions (Q0 R²=.016, log alpha R²=.104 -- see Table 6), smaller than the effect of individual factors (Q0 R²=.40, log alpha R²=.32 -- see Table 6 Model 2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="391" ht="13" customHeight="1">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Tewogbola2025-hiv-mhc</t>
+        </is>
+      </c>
+      <c r="B391" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>Journal of the Experimental Analysis of Behavior</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>10.1002/jeab.70038</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/jeab.70038</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>Peer-Reviewed</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>HIV vaccine</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>Health &amp; Prevention</t>
+        </is>
+      </c>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Between-subjects</t>
+        </is>
+      </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M391" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N391" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="O391" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="P391" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q391" t="inlineStr">
+        <is>
+          <t>Sexual and gender minority adults (Reddit- and LGBTQ+ community organization-recruited)</t>
+        </is>
+      </c>
+      <c r="R391" t="n">
+        <v>29.37</v>
+      </c>
+      <c r="S391" t="n">
+        <v>15</v>
+      </c>
+      <c r="T391" t="n">
+        <v>0</v>
+      </c>
+      <c r="U391" t="n">
+        <v>2000</v>
+      </c>
+      <c r="V391" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="W391" t="inlineStr">
+        <is>
+          <t>Koffarnus et al. exponentiated model</t>
+        </is>
+      </c>
+      <c r="X391" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Y391" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z391" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA391" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="AB391" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC391" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD391" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE391" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG391" t="n">
+        <v>4.48e-06</v>
+      </c>
+      <c r="AH391" t="n">
+        <v>77.77</v>
+      </c>
+      <c r="AI391" t="n">
+        <v>603</v>
+      </c>
+      <c r="AJ391" t="n">
+        <v>542.0700000000001</v>
+      </c>
+      <c r="AK391" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="AL391" t="inlineStr">
+        <is>
+          <t>Self-authored by the PI (PROMISE Labs Africa), with Eric A. Jacobs, Yueh-Ting Lee, and Ryan N. Redner (SIU Carbondale School of Psychological and Behavioral Sciences), Justin T. McDaniel (SIU School of Health Sciences), and Jebaraj Asirvatham (SIU School of Agricultural Sciences). Peer-reviewed (Journal of the Experimental Analysis of Behavior, 2025). Open-access status not confirmed -- no CC license visible on the article pages reviewed here, so marked No pending verification. Both experiments used the same 393 recruited sexual/gender-minority participants (Reddit + LGBTQ+ community organizations, U.S., aged 19+); Experiment 1 retained N=285 after exclusions, Experiment 2 retained N=236 (all Experiment-1 completers were invited into Experiment 2). 15 price points, $0-$2,000, VAS-slider purchase-likelihood task adapted from Hursh et al. (2020). This row: Experiment 2 (bundle-condition n=25 of N=236 total; Table 4's 9 per-bundle n's sum to 235, one short of the stated 236 -- discrepancy in the source, not corrected here), demand for a hypothetical HIV vaccine bundled with mental health counseling, values from Table 5. Bundling effects were subtle overall across the 9 conditions (Q0 R²=.016, log alpha R²=.104 -- see Table 6), smaller than the effect of individual factors (Q0 R²=.40, log alpha R²=.32 -- see Table 6 Model 2).</t>
+        </is>
+      </c>
+    </row>
     <row r="392" ht="13" customHeight="1"/>
     <row r="393" ht="13" customHeight="1"/>
     <row r="394" ht="13" customHeight="1"/>

--- a/HPT Resource Index.xlsx
+++ b/HPT Resource Index.xlsx
@@ -610,7 +610,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL391"/>
+  <dimension ref="A1:AL392"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="12.33203125" customWidth="1" min="1" max="1"/>
@@ -75186,7 +75186,171 @@
         </is>
       </c>
     </row>
-    <row r="392" ht="13" customHeight="1"/>
+    <row r="392" ht="13" customHeight="1">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Acuff2022-int</t>
+        </is>
+      </c>
+      <c r="B392" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>Experimental and Clinical Psychopharmacology</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>10.1037/pha0000459</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1037/pha0000459</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>Peer-Reviewed</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>Internet Access</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>Leisure &amp; Entertainment</t>
+        </is>
+      </c>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>Cross-sectional</t>
+        </is>
+      </c>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M392" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N392" t="inlineStr">
+        <is>
+          <t>United States; Argentina; Australia; Malaysia; United Kingdom; India</t>
+        </is>
+      </c>
+      <c r="O392" t="inlineStr">
+        <is>
+          <t>Multi-regional</t>
+        </is>
+      </c>
+      <c r="P392" t="n">
+        <v>1406</v>
+      </c>
+      <c r="Q392" t="inlineStr">
+        <is>
+          <t>College students (six-country sample)</t>
+        </is>
+      </c>
+      <c r="R392" t="n">
+        <v>20.92</v>
+      </c>
+      <c r="S392" t="n">
+        <v>25</v>
+      </c>
+      <c r="T392" t="n">
+        <v>0</v>
+      </c>
+      <c r="U392" t="n">
+        <v>100</v>
+      </c>
+      <c r="V392" t="inlineStr">
+        <is>
+          <t>USD (PPP-equivalized across countries)</t>
+        </is>
+      </c>
+      <c r="W392" t="inlineStr">
+        <is>
+          <t>Koffarnus et al. exponentiated model</t>
+        </is>
+      </c>
+      <c r="X392" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Y392" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z392" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA392" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB392" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC392" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD392" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE392" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF392" t="inlineStr">
+        <is>
+          <t>Omax (maximum expenditure, $30.19 PPP-USD, N-weighted across countries)</t>
+        </is>
+      </c>
+      <c r="AG392" t="n">
+        <v>0.01875</v>
+      </c>
+      <c r="AH392" t="n">
+        <v>15.13</v>
+      </c>
+      <c r="AI392" t="n">
+        <v>18.71</v>
+      </c>
+      <c r="AK392" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AL392" t="inlineStr">
+        <is>
+          <t>Not self-authored -- independent multi-site group (University of Memphis lead, with co-authors in Argentina, Australia, India, Malaysia, and the UK). Peer-reviewed (Experimental and Clinical Psychopharmacology); published online first 2021-04-29, print issue Vol. 30 No. 5 (2022) -- coded here as 2022 to match the print volume/issue. Open-access status not confirmed -- no CC license visible on the article pages reviewed, marked No pending verification. Cross-sectional, six-country college-student sample (United States n=217, Argentina n=300, Australia n=254, Malaysia n=323, United Kingdom n=173, India n=153 -- these six Table 1 n's sum to 1,420, slightly above the paper's stated total N=1,406; the paper's own footnote notes per-index exclusions differ slightly, e.g. 47 participants dropped from elasticity only for Stein's-criteria inconsistency, so per-index/per-country n's are not perfectly uniform). Prices were set in USD ($0-$100, 25 escalating points above the free/$0 anchor) then multiplied by each country's Purchasing Power Parity index (Argentina 13.56 pesos/USD; Australia 1.44 AUD/USD; Malaysia 1.46 Ringgit/USD; UK 0.7 GBP/USD; India 18.04 Rupees/USD, as of the 2018 study launch) so consumption is comparable at equivalent real purchasing power -- currency is nominally USD but PPP-equivalized, not raw local currency. Q0/Breakpoint/Omax/Elasticity here are the simple N-weighted mean of Table 1's six country-level means (weights = each country's Table 1 n) -- a considerable simplification, since the paper's actual key finding is significant CROSS-COUNTRY differences on nearly every index (all F/chi-square tests in Table 1 significant at p&lt;.02 or lower) and significant differences by GDP-per-capita group, sex at birth, and income (Table 3) -- see Table 1 (by country) and Table 3 (by GDP group/sex/income) for the real breakdown, not reproduced as separate rows here. Elasticity mapped to this index's alpha field and Intensity mapped to Q0 -- both are the paper's own terms for the exponentiated-model parameters (Koffarnus et al., 2015). No Pmax reported (only Intensity/Breakpoint/Omax/Elasticity used); Omax entered as text under Other since this schema's Pmax field is a different index (price of max expenditure, not reported here) -- Omax value above is also the N-weighted pooled mean. k=2.08, calculated empirically per Koffarnus et al. (2015) from the log10-transformed consumption range, not fit per individual. R2: participant-level full-sample mean R2=.94 (median .96); aggregate full-sample R2=.97 (used as mean_r2 here); country-level aggregate R2 ranged .95-.99 (not broken out per country in this row). Demand indices also feed a larger structural equation model relating Internet demand, delay discounting, and alternative reinforcement to harmful Internet use, smartphone addiction, online gaming, and Internet sexual behavior (Figure 3) -- out of this index's HPT-demand scope, not coded here.</t>
+        </is>
+      </c>
+    </row>
     <row r="393" ht="13" customHeight="1"/>
     <row r="394" ht="13" customHeight="1"/>
     <row r="395" ht="13" customHeight="1"/>

--- a/HPT Resource Index.xlsx
+++ b/HPT Resource Index.xlsx
@@ -610,7 +610,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL392"/>
+  <dimension ref="A1:AL397"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="12.33203125" customWidth="1" min="1" max="1"/>
@@ -75351,11 +75351,797 @@
         </is>
       </c>
     </row>
-    <row r="393" ht="13" customHeight="1"/>
-    <row r="394" ht="13" customHeight="1"/>
-    <row r="395" ht="13" customHeight="1"/>
-    <row r="396" ht="13" customHeight="1"/>
-    <row r="397" ht="13" customHeight="1"/>
+    <row r="393" ht="13" customHeight="1">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>PerezGonzalez2022-cig</t>
+        </is>
+      </c>
+      <c r="B393" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>Journal of Behavior, Health &amp; Social Issues</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>10.22201/fesi.20070780e.2022.14.2.80401</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>http://dx.doi.org/10.22201/fesi.20070780e.2022.14.2.80401</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>Peer-Reviewed</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>Cigarettes</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>Tobacco &amp; Nicotine</t>
+        </is>
+      </c>
+      <c r="J393" t="inlineStr">
+        <is>
+          <t>Cross-sectional</t>
+        </is>
+      </c>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M393" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N393" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="O393" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="P393" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q393" t="inlineStr">
+        <is>
+          <t>Adult daily/occasional smokers (Mexico City, online-recruited)</t>
+        </is>
+      </c>
+      <c r="R393" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="S393" t="n">
+        <v>19</v>
+      </c>
+      <c r="T393" t="n">
+        <v>0</v>
+      </c>
+      <c r="U393" t="n">
+        <v>250</v>
+      </c>
+      <c r="V393" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="W393" t="inlineStr">
+        <is>
+          <t>Hursh &amp; Silberberg exponential model</t>
+        </is>
+      </c>
+      <c r="X393" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Y393" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z393" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA393" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="AB393" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC393" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD393" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE393" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG393" t="n">
+        <v>0.0034</v>
+      </c>
+      <c r="AK393" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AL393" t="inlineStr">
+        <is>
+          <t>Not self-authored -- independent Mexican group (UNAM, FES Iztacala + Facultad de Psicologia). Peer-reviewed (Journal of Behavior, Health &amp; Social Issues, UNAM). Cross-sectional online study (Google Forms), N=38 recruited Mexico City daily/occasional smokers (26 men, 12 women; mean age 35.5, SD=10.8; mean cigarettes/day=8, SD=7.6; mean years smoking=14.5, SD=9.7; Fagerstrom nicotine dependence: 73.7% low, 18.4% medium, 7.9% high). Participants completed three sequential purchase tasks (conventional cigarette, e-cigarette, and a cross-demand task) with the same 19 escalating MXN prices ($0/free, $2-$250) adapted from MacKillop et al. (2008). This row: the conventional-cigarette own-price purchase task (Figure 1). Data from 3 of the 38 participants were dropped for nonsystematic responding (no consumption decrease despite price increases), leaving N=35 for this task's demand curve. Alpha and R2 are the group-level exponential-model fit shown in Figure 1; the paper does not report numeric group means/SDs for Q0 (intensity), Omax, breakpoint, or Pmax anywhere in the text -- these indices were used only in a correlation matrix (Table 1) and two regression models (Tables 2-3, predicting self-reported consumption pattern and Fagerstrom dependence score from the demand indices) without ever stating their own descriptive means, so mean_q0/mean_breakpoint/mean_pmax are left blank here rather than estimated from the log-log graph. A separate N=20 subsample who completed both the conventional and e-cigarette tasks showed a slightly different, equal-across-products alpha of 0.0031 for both cigarette types (Figure 3) -- not used here since Figure 1's full-sample (N=35) value is the more representative aggregate for this row; see the paper for the Figure 3 comparison.</t>
+        </is>
+      </c>
+    </row>
+    <row r="394" ht="13" customHeight="1">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>PerezGonzalez2022-ecig</t>
+        </is>
+      </c>
+      <c r="B394" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Journal of Behavior, Health &amp; Social Issues</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>10.22201/fesi.20070780e.2022.14.2.80401</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>http://dx.doi.org/10.22201/fesi.20070780e.2022.14.2.80401</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>Peer-Reviewed</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>E-cigarettes</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>Tobacco &amp; Nicotine</t>
+        </is>
+      </c>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>Cross-sectional</t>
+        </is>
+      </c>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M394" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N394" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="O394" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="P394" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q394" t="inlineStr">
+        <is>
+          <t>Adult daily/occasional smokers (Mexico City, online-recruited)</t>
+        </is>
+      </c>
+      <c r="R394" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="S394" t="n">
+        <v>19</v>
+      </c>
+      <c r="T394" t="n">
+        <v>0</v>
+      </c>
+      <c r="U394" t="n">
+        <v>250</v>
+      </c>
+      <c r="V394" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="W394" t="inlineStr">
+        <is>
+          <t>Hursh &amp; Silberberg exponential model</t>
+        </is>
+      </c>
+      <c r="X394" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Y394" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z394" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA394" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="AB394" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC394" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD394" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE394" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF394" t="inlineStr">
+        <is>
+          <t>Cross-price elasticity (substitution slope, beta=0.026) for e-cigarette consumption when conventional cigarette price was fixed at $5 (cross-demand task, Figure 4, N=20)</t>
+        </is>
+      </c>
+      <c r="AG394" t="n">
+        <v>0.0034</v>
+      </c>
+      <c r="AK394" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AL394" t="inlineStr">
+        <is>
+          <t>Not self-authored -- independent Mexican group (UNAM, FES Iztacala + Facultad de Psicologia). Peer-reviewed (Journal of Behavior, Health &amp; Social Issues, UNAM). Same study and same 38-participant Mexican smoker sample as the companion conventional-cigarette row (PerezGonzalez2022-cig) -- same 19-price MXN schedule ($0-$250), adapted from MacKillop et al. (2008), but instructions specified 10 puffs/"vapeadas" = 1 cigarette-equivalent to equate units with the conventional-cigarette task. This row: the e-cigarette own-price purchase task (Figure 2). Of the 38 participants, only 20 showed nonzero e-cigarette demand and were retained for curve-fitting (18 were excluded for null demand -- 47.4% of the full sample reported no e-cigarette demand at any price, consistent with only 26.3% of the sample having ever used an e-cigarette). Alpha and R2 are the group-level exponential-model fit shown in Figure 2; as with the conventional-cigarette row, the paper never reports numeric group means/SDs for Q0, Omax, breakpoint, or Pmax, so those fields are left blank rather than estimated from the log-log graph. A third, separate cross-demand task (Figure 4) fixed the conventional cigarette at a constant $5 price while e-cigarette price still escalated, to test substitution; this produced a positive cross-price elasticity (beta=0.026, entered under Other below) -- the abstract states this value as "0.0026," which appears to be a decimal-place typo against the matching figure and body-text value of 0.026 used here. Despite the positive cross-elasticity, the authors note it falls well short of the &gt;0.20 threshold they cite as indicating meaningful substitution (only 3 of 38 individual participants exceeded that threshold), so they do not treat this as strong evidence of substitutability between the two products.</t>
+        </is>
+      </c>
+    </row>
+    <row r="395" ht="13" customHeight="1">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>DoNascimento2025-con</t>
+        </is>
+      </c>
+      <c r="B395" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>Revista Brasileira de Analise do Comportamento (ReBAC)</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>10.18542/rebac.v21i2.19777</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>http://dx.doi.org/10.18542/rebac.v21i2.19777</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>Peer-Reviewed</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>Condoms</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>Health &amp; Prevention</t>
+        </is>
+      </c>
+      <c r="J395" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Within-subjects</t>
+        </is>
+      </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M395" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N395" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="O395" t="inlineStr">
+        <is>
+          <t>South America</t>
+        </is>
+      </c>
+      <c r="P395" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q395" t="inlineStr">
+        <is>
+          <t>Heterosexual male university students, sexually active, ages 18-26</t>
+        </is>
+      </c>
+      <c r="S395" t="n">
+        <v>17</v>
+      </c>
+      <c r="T395" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U395" t="n">
+        <v>150</v>
+      </c>
+      <c r="V395" t="inlineStr">
+        <is>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="W395" t="inlineStr">
+        <is>
+          <t>Koffarnus et al. exponentiated model</t>
+        </is>
+      </c>
+      <c r="X395" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="Y395" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z395" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA395" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="AB395" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC395" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD395" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE395" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL395" t="inlineStr">
+        <is>
+          <t>Not self-authored -- independent Brazilian group (Centro de Ensino Unificado de Brasilia). Peer-reviewed (Revista Brasileira de Analise do Comportamento / Brazilian Journal of Behavior Analysis, ReBAC), open access (CC BY-NC 4.0). Within-subject design (delineamento intrassujeito), 2 (risk type: STI vs. unplanned pregnancy) x 2 (scenario: neutral vs. negative/regret-framed hypothetical vignette about a friend) x 2 (partner attractiveness: high vs. low, selected/ranked by each participant from 20 photos), all 8 cells completed by every participant. N=10 heterosexual male university students, sexually active, ages 18-26 (15 recruited, 5 excluded for inconsistent/nonsystematic delay-discounting data in 2+ of 8 discounting tasks per Stein et al. (2015)-style criteria; demand-task data were separately screened with the same criteria and no participants were excluded on that basis). Condom Purchase Task adapted from Strickland et al. (2020), 17 escalating BRL prices (R$0.50-R$150.00), Koffarnus et al. (2015) exponential model fit via the beezdemand R package. This paper's Results section reports NO numeric group-level Q0, alpha, R2, breakpoint, or Pmax values anywhere in the main text -- only Figure 5 (a per-condition purchase-probability-vs-price graph, not digitized here) and a long series of Wilcoxon Signed-Rank tests comparing alpha (and AUC, a delay-discounting measure -- not a demand index) pairwise across conditions/scenarios/attractiveness levels, reported only as z/p/rank-biserial effect size, never as a group mean or SD. Individual-level raw purchase-probability-by-price data (not fitted Q0/alpha/R2 parameters) for all 10 participants across all 8 conditions are available in the paper's own supplementary GitHub repo (github.com/edutsviegas-lang/Pesquisa-Desconto-e-Demanda-IST---Gravidez), but fitting demand curves to that raw data would be an independent secondary analysis not reported by the authors, so it was not done here -- all demand-index mean fields below are left blank by design, not omitted by oversight. Q0 is part of the model equation used but was not itself analyzed or reported as an outcome (only alpha was); breakpoint and Pmax are not mentioned anywhere outside the introduction's general discussion of demand theory. The study's headline findings were about impulsivity (delay discounting, measured via AUC) and demand (alpha) both being reduced by a negative/regret-framed scenario relative to neutral, with some condition-specific differences between STI-risk and pregnancy-risk framing and partner attractiveness -- see the paper directly (Figures 4-5, pp. 206-209) for the full qualitative pattern of results.</t>
+        </is>
+      </c>
+    </row>
+    <row r="396" ht="13" customHeight="1">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>Schwartz2022-aw</t>
+        </is>
+      </c>
+      <c r="B396" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>Managerial and Decision Economics</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>10.1002/mde.3558</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/mde.3558</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>Peer-Reviewed</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>Apple Watch</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>Leisure &amp; Entertainment</t>
+        </is>
+      </c>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M396" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N396" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="O396" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="P396" t="n">
+        <v>357</v>
+      </c>
+      <c r="Q396" t="inlineStr">
+        <is>
+          <t>Amazon mTurk workers (US-located adults)</t>
+        </is>
+      </c>
+      <c r="R396" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="S396" t="n">
+        <v>9</v>
+      </c>
+      <c r="T396" t="n">
+        <v>0</v>
+      </c>
+      <c r="U396" t="n">
+        <v>1500</v>
+      </c>
+      <c r="V396" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="W396" t="inlineStr">
+        <is>
+          <t>Zero-bounded exponential model (Gilroy et al., 2021)</t>
+        </is>
+      </c>
+      <c r="X396" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Y396" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z396" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA396" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AB396" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC396" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD396" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE396" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF396" t="inlineStr">
+        <is>
+          <t>Essential Value (EV=1/[100 x alpha]) = 265.25, calculated from this row's alpha</t>
+        </is>
+      </c>
+      <c r="AG396" t="n">
+        <v>3.77e-05</v>
+      </c>
+      <c r="AH396" t="inlineStr">
+        <is>
+          <t>100 (ceiling-constrained by model fitting, not freely estimated)</t>
+        </is>
+      </c>
+      <c r="AJ396" t="n">
+        <v>151.15</v>
+      </c>
+      <c r="AK396" t="n">
+        <v>0.9733000000000001</v>
+      </c>
+      <c r="AL396" t="inlineStr">
+        <is>
+          <t>Not self-authored -- independent group (Institutes for Behavior Resources / Johns Hopkins). Peer-reviewed (Managerial and Decision Economics). Open-access status not confirmed -- no article-specific CC license visible beyond Wiley's generic OA-articles boilerplate, marked No pending verification. Amazon mTurk sample (US-located adults, mean age 36.6 -- reported as "±0.47," which given the sample size is almost certainly a standard error, not an SD). 518 participants responded across 3 data-collection iterations (June 2019-January 2020) for the Apple Watch, of which the largest analyzable subsample (standard Apple Watch, after Stein et al. (2015) nonsystematic-data exclusions) was N=357 -- used as this row's sample_size. Two additional within-brand feature variants were tested: Apple Watch + Sleep Tracking (N=273) and Apple Watch + Extended Battery Life (N=267); a reliability check found no significant differences in demand across the 3 data-collection iterations for any of the 3 products (justifying a single shared alpha per product), and critically, an F-test found NO significant difference in demand between the standard Apple Watch and either feature-added variant (F[4,21]=0.14, p=.97) -- so this single row represents all three Apple Watch variants pooled, consistent with the paper's own conclusion that added features didn't change valuation. Per-product shared-alpha values from Figure 1 were: standard Apple Watch alpha=3.77e-05 (R2 across 3 iterations: .99/.97/.96), + Sleep Tracking alpha=3.65e-05 (R2: .98/.98/.97), + Extended Battery alpha=3.49e-05 (R2: .97/.97/.96) -- this row uses the standard Apple Watch's alpha (3.77e-05) and the mean R2 across its 3 iterations (.9733) as the representative values, since it is the base/reference product; the paper's own general statement ('average R2 of 0.99') is close to but not identical to this and isn't used verbatim since it's unclear whether it covers SW/BW too. Q0 was hard-ceiling-constrained to exactly 100 by the fitting procedure itself (the model would not allow values above the survey's 100% maximum) -- NOT a freely estimated demand-intensity value, unlike Q0 elsewhere in this index. Pmax=151.15 is explicitly reported in the text as a single pooled value 'for the Apple watch curves' (i.e., across all 3 feature variants, not product-specific). Essential Value (EV = 1/[100 x alpha]) is a named index in this paper (unlike most entries in this dataset) -- entered under Other as EV=1/(100 x 3.77e-05)=265.25, calculated from the paper's own alpha and its own stated EV formula (a direct value isn't given for the pooled/base sample, only for demographic subgroups in Figure 3, e.g. iPhone owners EV=330 vs non-owners EV=184 for the standard watch, and Apple Watch owners EV=455 vs other-watch owners EV=210 -- both differences statistically significant, the paper's main finding being that HPT demand is sensitive to brand loyalty/ownership but not to hypothetical added features). Demand model is the zero-bounded exponential (ZBE; Gilroy et al., 2021), which has no k scaling-constant parameter (unlike the Koffarnus/Hursh-Silberberg models used elsewhere in this index) -- has_k marked N/A rather than NR. Participant assignment was mixed across iterations: iterations 1-2 randomly split participants into a feature-HPT group vs. an unrelated app-purchase group (not analyzed here), while iteration 3 had all participants complete all 3 Apple Watch HPTs within-subject.</t>
+        </is>
+      </c>
+    </row>
+    <row r="397" ht="13" customHeight="1">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>Schwartz2022-fv</t>
+        </is>
+      </c>
+      <c r="B397" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Managerial and Decision Economics</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>10.1002/mde.3558</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/mde.3558</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>Peer-Reviewed</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>Fitbit Versa</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>Leisure &amp; Entertainment</t>
+        </is>
+      </c>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M397" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N397" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="O397" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="P397" t="n">
+        <v>79</v>
+      </c>
+      <c r="Q397" t="inlineStr">
+        <is>
+          <t>Amazon mTurk workers (US-located adults)</t>
+        </is>
+      </c>
+      <c r="R397" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="S397" t="n">
+        <v>9</v>
+      </c>
+      <c r="T397" t="n">
+        <v>0</v>
+      </c>
+      <c r="U397" t="n">
+        <v>1200</v>
+      </c>
+      <c r="V397" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="W397" t="inlineStr">
+        <is>
+          <t>Zero-bounded exponential model (Gilroy et al., 2021)</t>
+        </is>
+      </c>
+      <c r="X397" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Y397" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z397" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA397" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AB397" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC397" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD397" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE397" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF397" t="inlineStr">
+        <is>
+          <t>Essential Value (EV) is a named index used in this paper but no numeric value is reported for Fitbit</t>
+        </is>
+      </c>
+      <c r="AJ397" t="n">
+        <v>118.63</v>
+      </c>
+      <c r="AL397" t="inlineStr">
+        <is>
+          <t>Not self-authored -- independent group (Institutes for Behavior Resources / Johns Hopkins). Peer-reviewed (Managerial and Decision Economics). Open-access status not confirmed, marked No pending verification. Companion row to Apple Watch (Schwartz2022-aw) from the same study and same mTurk sample (US-located adults, mean age 36.6, reported as "±0.47" which is almost certainly SE not SD) -- only 1 data-collection iteration was run for Fitbit (vs. 3 for Apple Watch), so no iteration-reliability table exists. This row represents the standard Fitbit Versa (N=79, the largest Fitbit subsample after Stein et al. (2015) exclusions); two feature variants were also tested -- Fitbit + Sleep Debt Tracker (N=40) and Fitbit + Extended Battery (N=39) -- and, as with the Apple Watch, an F-test found no significant difference in demand between the standard Fitbit and either feature-added variant (F[4,21]=1.02, p=.42), so all three are treated as one pooled commodity here. Unlike the Apple Watch, this paper reports NO numeric alpha, Q0, or R2 value anywhere in the text for any Fitbit product -- only a demand-curve graph (Figure 2b) without an accompanying parameter table, and p-values from significance tests comparing Fitbit demand across iPhone-owner/Apple-Watch-owner subgroups (all non-significant, ps&gt;.05, unlike the equivalent Apple Watch comparisons which WERE significant -- i.e., brand loyalty affected Apple Watch demand but not Fitbit demand). mean_alpha, mean_q0, and mean_r2 are therefore left blank rather than estimated from the graph. Pmax=118.63 is the one numeric index given, reported in the text as a single pooled value 'for the Fitbit curves' (across all 3 feature variants). Demand model is the zero-bounded exponential (ZBE; Gilroy et al., 2021), which has no k scaling-constant parameter -- has_k marked N/A. Essential Value is a named index in this paper (has_essential_value=Yes) but, as with alpha/Q0/R2, no numeric EV value is given anywhere for the Fitbit products specifically.</t>
+        </is>
+      </c>
+    </row>
     <row r="398" ht="13" customHeight="1"/>
     <row r="399" ht="13" customHeight="1"/>
     <row r="400" ht="13" customHeight="1"/>
